--- a/artfynd/A 30913-2024 artfynd.xlsx
+++ b/artfynd/A 30913-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118883880</v>
+        <v>118883876</v>
       </c>
       <c r="B2" t="n">
-        <v>97853</v>
+        <v>56502</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,34 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +735,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567540</v>
+        <v>567560</v>
       </c>
       <c r="R2" t="n">
-        <v>6689455</v>
+        <v>6689419</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -760,18 +773,12 @@
           <t>2024-08-03</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118883878</v>
+        <v>118883877</v>
       </c>
       <c r="B3" t="n">
-        <v>57306</v>
+        <v>57443</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,27 +813,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567546</v>
+        <v>567553</v>
       </c>
       <c r="R3" t="n">
-        <v>6689435</v>
+        <v>6689369</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -897,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118883876</v>
+        <v>118883881</v>
       </c>
       <c r="B4" t="n">
-        <v>56502</v>
+        <v>97853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,58 +916,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rönningen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567560</v>
+        <v>567517</v>
       </c>
       <c r="R4" t="n">
-        <v>6689419</v>
+        <v>6689609</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1019,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118883875</v>
+        <v>118883879</v>
       </c>
       <c r="B5" t="n">
-        <v>90511</v>
+        <v>90006</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,25 +1027,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>2051</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567489</v>
+        <v>567457</v>
       </c>
       <c r="R5" t="n">
-        <v>6689561</v>
+        <v>6689489</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1121,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118883879</v>
+        <v>118883878</v>
       </c>
       <c r="B6" t="n">
-        <v>90006</v>
+        <v>57306</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,38 +1129,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2051</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rönningen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567457</v>
+        <v>567546</v>
       </c>
       <c r="R6" t="n">
-        <v>6689489</v>
+        <v>6689435</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1223,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118883877</v>
+        <v>118883875</v>
       </c>
       <c r="B7" t="n">
-        <v>57443</v>
+        <v>90511</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1239,39 +1240,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rönningen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567553</v>
+        <v>567489</v>
       </c>
       <c r="R7" t="n">
-        <v>6689369</v>
+        <v>6689561</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1330,7 +1326,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118883881</v>
+        <v>118883880</v>
       </c>
       <c r="B8" t="n">
         <v>97853</v>
@@ -1363,26 +1359,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rönningen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567517</v>
+        <v>567540</v>
       </c>
       <c r="R8" t="n">
-        <v>6689609</v>
+        <v>6689455</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1417,12 +1411,18 @@
           <t>2024-08-03</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
